--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.28413160497409</v>
+        <v>11.09617138580829</v>
       </c>
       <c r="D2" t="n">
-        <v>70.05526514618958</v>
+        <v>11.38398058625581</v>
       </c>
       <c r="E2" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F2" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.74611834996296</v>
+        <v>8.571244231868981</v>
       </c>
       <c r="D3" t="n">
-        <v>52.61695979108094</v>
+        <v>8.550255966050655</v>
       </c>
       <c r="E3" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F3" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.09665745321826</v>
+        <v>7.490706836147968</v>
       </c>
       <c r="D4" t="n">
-        <v>42.32316150761897</v>
+        <v>6.877513744988083</v>
       </c>
       <c r="E4" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F4" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.74382208246935</v>
+        <v>5.80837108840127</v>
       </c>
       <c r="D5" t="n">
-        <v>30.59150128310276</v>
+        <v>4.971118958504198</v>
       </c>
       <c r="E5" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F5" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.92058658791967</v>
+        <v>5.837095320536947</v>
       </c>
       <c r="D6" t="n">
-        <v>13.80883826118596</v>
+        <v>2.243936217442718</v>
       </c>
       <c r="E6" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F6" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.21186195864986</v>
+        <v>9.296927568280601</v>
       </c>
       <c r="D7" t="n">
-        <v>58.95347924075057</v>
+        <v>9.579940376621968</v>
       </c>
       <c r="E7" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F7" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.08192172422348</v>
+        <v>6.838312280186315</v>
       </c>
       <c r="D8" t="n">
-        <v>16.76305461424021</v>
+        <v>2.723996374814035</v>
       </c>
       <c r="E8" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F8" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.87065434536991</v>
+        <v>3.55398133112261</v>
       </c>
       <c r="D9" t="n">
-        <v>6.5</v>
+        <v>1.05625</v>
       </c>
       <c r="E9" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F9" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.9387418273298</v>
+        <v>5.515045546941093</v>
       </c>
       <c r="D10" t="n">
-        <v>17.74353937029158</v>
+        <v>2.883325147672381</v>
       </c>
       <c r="E10" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F10" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.750365390144299</v>
+        <v>1.259434375898449</v>
       </c>
       <c r="D11" t="n">
-        <v>7.454771250454805</v>
+        <v>1.211400328198906</v>
       </c>
       <c r="E11" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F11" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.91325256230503</v>
+        <v>5.185903541374567</v>
       </c>
       <c r="D12" t="n">
-        <v>32.93926817159081</v>
+        <v>5.352631077883507</v>
       </c>
       <c r="E12" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F12" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.43771587155799</v>
+        <v>3.808628829128174</v>
       </c>
       <c r="D13" t="n">
-        <v>21.8197315085542</v>
+        <v>3.545706370140058</v>
       </c>
       <c r="E13" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F13" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>57.91242895165716</v>
+        <v>9.410769704644288</v>
       </c>
       <c r="D14" t="n">
-        <v>53.41348144429457</v>
+        <v>8.679690734697868</v>
       </c>
       <c r="E14" t="n">
-        <v>16.16972630272678</v>
+        <v>2.627580524193101</v>
       </c>
       <c r="F14" t="n">
-        <v>20.16127583031408</v>
+        <v>3.276207322426038</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
